--- a/Connector Testy Akceptacyjne.xlsx
+++ b/Connector Testy Akceptacyjne.xlsx
@@ -9,7 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="Prototyp 1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Checklista TAP1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Prototyp 2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Checklista TAP1" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -35,7 +36,7 @@
     <t xml:space="preserve">Oraz</t>
   </si>
   <si>
-    <t xml:space="preserve">Kedy</t>
+    <t xml:space="preserve">Kiedy</t>
   </si>
   <si>
     <t xml:space="preserve">Wtedy</t>
@@ -235,6 +236,57 @@
   </si>
   <si>
     <t xml:space="preserve">jego reprezentacja wizualna zostaje niezmieniona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obiekty mogą być połączone relacjami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stworzone dowolne dwa obiekty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">użytkownik kliknie dedykowany przycisk łączenia relacjami i wskaże dwa obiekty</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> obiekty zostaną połączone relacją</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Połączenie relacjami jest widoczne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zostanie wyświetlona linia symbolizująca relację</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relacje można usunąć</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dwa obiekty połączone relacją</t>
+  </si>
+  <si>
+    <t xml:space="preserve">użytkownik zaznaczy relację i kliknie przycisk usunięcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relacja i jej wizualizacja zostaną usunięte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie można utworzyć więcej niż jednej relacji w jednym kierunku między każdymi dwoma obiektami.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">użytkownik spróbuje połączyć obiekty ponownie relacją w tym samym kierunku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">użytkownik zostanie powstrzymany lub nie będzie miał takiej możliwości</t>
   </si>
   <si>
     <t xml:space="preserve">Rezultat 25.09.'25</t>
@@ -580,7 +632,21 @@
     <tableColumn id="2" name="Nazwa"/>
     <tableColumn id="3" name="Mając"/>
     <tableColumn id="4" name="Oraz"/>
-    <tableColumn id="5" name="Kedy"/>
+    <tableColumn id="5" name="Kiedy"/>
+    <tableColumn id="6" name="Wtedy"/>
+    <tableColumn id="7" name="I" totalsRowFunction="sum"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1_2" displayName="Table1_2" ref="A1:G5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="7">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Nazwa"/>
+    <tableColumn id="3" name="Mając"/>
+    <tableColumn id="4" name="Oraz"/>
+    <tableColumn id="5" name="Kiedy"/>
     <tableColumn id="6" name="Wtedy"/>
     <tableColumn id="7" name="I" totalsRowFunction="sum"/>
   </tableColumns>
@@ -770,13 +836,13 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.6" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="57.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="54.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="53.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="51.87"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -860,7 +926,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
@@ -1011,8 +1077,144 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G1048576"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.6" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="49.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="51.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="2.33"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="overThenDown" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="13.48828125" defaultRowHeight="14.6" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="14.6" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.37"/>
@@ -1025,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1036,7 +1238,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C2" s="6"/>
     </row>
@@ -1045,7 +1247,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C3" s="6"/>
     </row>
@@ -1054,7 +1256,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6"/>
     </row>
@@ -1063,7 +1265,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C5" s="6"/>
     </row>
@@ -1072,7 +1274,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C6" s="6"/>
     </row>
@@ -1081,10 +1283,10 @@
         <v>33</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1092,7 +1294,7 @@
         <v>38</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C8" s="6"/>
     </row>
@@ -1101,7 +1303,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -1110,13 +1312,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="14.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">COUNTIF(B2:B10, "pass")/ROWS(B2:B10)</f>
